--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra899719033a3488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652be49ede5e479b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0074b3b9854b4180"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7648959c8d0a4519"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495a5ee2775f4c8d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9a6f1d35d4b4e44"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652be49ede5e479b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb730ce28aab405c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7648959c8d0a4519"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbaa925a47adc41fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9a6f1d35d4b4e44"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc891041e28174913"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb730ce28aab405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc4d2621e3d324b6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbaa925a47adc41fb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R016d7fe52d3544e4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc891041e28174913"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90821194ba0b4db2"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc4d2621e3d324b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b5625a65b7046b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R016d7fe52d3544e4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8526d2ca62a41f4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90821194ba0b4db2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf49194423ab4c7c"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b5625a65b7046b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09e2e1e2dfeb4095"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8526d2ca62a41f4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b43d8619639407c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf49194423ab4c7c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc11992396bc7478f"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09e2e1e2dfeb4095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6166bb67279a4ad3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b43d8619639407c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02dd4ef4ae55405b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc11992396bc7478f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c89b22bf5d4d29"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6166bb67279a4ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd721fc6c4d654c12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02dd4ef4ae55405b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f1b2ea3b6714352"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c89b22bf5d4d29"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5805565ed1254274"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd721fc6c4d654c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ed1ff95558c4f37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f1b2ea3b6714352"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Radee52537b0b4472"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5805565ed1254274"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc912b62ea3dd47ca"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ed1ff95558c4f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53a8adebe18d4e27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Radee52537b0b4472"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff21e4aaf64c46cc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc912b62ea3dd47ca"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54391fe7fe54963"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53a8adebe18d4e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R218969d23abc485a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff21e4aaf64c46cc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8550726af81478d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54391fe7fe54963"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb33983480b954b41"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R218969d23abc485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd008d0189af2490c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8550726af81478d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02838df2305a4e11"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb33983480b954b41"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88cbac4e687f4645"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd008d0189af2490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6af08a1afcd74d5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02838df2305a4e11"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R944cf4ceaf594a62"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88cbac4e687f4645"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reda829614f6e4de5"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6af08a1afcd74d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4ceb86ff7054c83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R944cf4ceaf594a62"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R676fa4782ed749be"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reda829614f6e4de5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra48185f01ac74e35"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4ceb86ff7054c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R79206971a9934b60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R676fa4782ed749be"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R871c1e07b6764194"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra48185f01ac74e35"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb483e896edb44962"/>
 </x:worksheet>
 </file>